--- a/activityAnalysis/US_SYS_Champs.xlsx
+++ b/activityAnalysis/US_SYS_Champs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rachaelnaphtal/Documents/JudgingAnalysis/activityAnalysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDDDB47-1BC7-FD4E-A669-2121ED06A700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D602640-4798-D047-ACFE-E9D2D14850C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16400" yWindow="940" windowWidth="13000" windowHeight="16120" xr2:uid="{2A00EA02-28DE-4344-A5F0-0970F91D8254}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="173">
   <si>
     <t>Name</t>
   </si>
@@ -553,6 +553,9 @@
   <si>
     <t>Marie Pearce</t>
   </si>
+  <si>
+    <t>Ashley Renard</t>
+  </si>
 </sst>
 </file>
 
@@ -3559,12 +3562,8 @@
         <v>20</v>
       </c>
       <c r="U18" s="2"/>
-      <c r="V18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="2" t="s">
         <v>30</v>
@@ -3948,7 +3947,7 @@
         <v>49</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="U21" s="2"/>
       <c r="V21" s="2" t="s">
@@ -3973,7 +3972,7 @@
       </c>
       <c r="AD21" s="2"/>
       <c r="AE21" s="2" t="s">
-        <v>103</v>
+        <v>172</v>
       </c>
       <c r="AF21" s="2" t="s">
         <v>8</v>
@@ -4603,11 +4602,19 @@
         <v>114</v>
       </c>
       <c r="AA26" s="2"/>
-      <c r="AB26" s="2"/>
-      <c r="AC26" s="2"/>
+      <c r="AB26" t="s">
+        <v>2</v>
+      </c>
+      <c r="AC26" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="AD26" s="2"/>
-      <c r="AE26" s="2"/>
-      <c r="AF26" s="2"/>
+      <c r="AE26" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF26" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="AG26" s="2"/>
       <c r="AH26" s="2"/>
       <c r="AI26" s="2"/>
@@ -4695,11 +4702,19 @@
         <v>8</v>
       </c>
       <c r="AA27" s="2"/>
-      <c r="AB27" s="2"/>
-      <c r="AC27" s="2"/>
+      <c r="AB27" t="s">
+        <v>6</v>
+      </c>
+      <c r="AC27" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="AD27" s="2"/>
-      <c r="AE27" s="2"/>
-      <c r="AF27" s="2"/>
+      <c r="AE27" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF27" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="AG27" s="2"/>
       <c r="AH27" s="2"/>
       <c r="AI27" s="2"/>
@@ -4780,8 +4795,12 @@
       <c r="V28" s="2"/>
       <c r="W28" s="2"/>
       <c r="X28" s="2"/>
-      <c r="Y28" s="2"/>
-      <c r="Z28" s="2"/>
+      <c r="Y28" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z28" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="AA28" s="2"/>
       <c r="AB28" s="2"/>
       <c r="AC28" s="2"/>
@@ -5664,8 +5683,8 @@
         <v>20</v>
       </c>
       <c r="L40" s="2"/>
-      <c r="M40" s="2" t="s">
-        <v>105</v>
+      <c r="M40" t="s">
+        <v>12</v>
       </c>
       <c r="N40" s="3" t="s">
         <v>20</v>
@@ -5727,15 +5746,15 @@
         <v>20</v>
       </c>
       <c r="I41" s="2"/>
-      <c r="J41" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K41" s="3" t="s">
+      <c r="J41" s="2"/>
+      <c r="K41" s="3"/>
+      <c r="L41" s="2"/>
+      <c r="M41" t="s">
+        <v>13</v>
+      </c>
+      <c r="N41" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" s="2"/>
       <c r="Q41" s="2"/>
@@ -5779,8 +5798,12 @@
         <v>20</v>
       </c>
       <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
+      <c r="D42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="F42" s="2"/>
       <c r="G42" s="2" t="s">
         <v>12</v>
@@ -5841,8 +5864,12 @@
         <v>20</v>
       </c>
       <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
+      <c r="D43" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="F43" s="2"/>
       <c r="G43" s="2" t="s">
         <v>76</v>
@@ -5903,8 +5930,12 @@
         <v>20</v>
       </c>
       <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
+      <c r="D44" t="s">
+        <v>2</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2" t="s">
         <v>2</v>
@@ -5916,8 +5947,8 @@
       <c r="J44" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="K44" s="2" t="s">
-        <v>104</v>
+      <c r="K44" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -5967,8 +5998,12 @@
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
+      <c r="J45" t="s">
+        <v>2</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -6021,8 +6056,12 @@
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
+      <c r="J46" t="s">
+        <v>11</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -6224,8 +6263,12 @@
       <c r="AV49" s="2"/>
     </row>
     <row r="50" spans="1:48">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
+      <c r="A50" t="s">
+        <v>2</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
@@ -6274,8 +6317,12 @@
       <c r="AV50" s="2"/>
     </row>
     <row r="51" spans="1:48">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
+      <c r="A51" t="s">
+        <v>2</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -6324,8 +6371,12 @@
       <c r="AV51" s="2"/>
     </row>
     <row r="52" spans="1:48">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
+      <c r="A52" t="s">
+        <v>120</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -6374,8 +6425,12 @@
       <c r="AV52" s="2"/>
     </row>
     <row r="53" spans="1:48">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
+      <c r="A53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
